--- a/BASE_HISTORICA_AGENDAMENTOS.xlsx
+++ b/BASE_HISTORICA_AGENDAMENTOS.xlsx
@@ -415,7 +415,15 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Servico</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/BASE_HISTORICA_AGENDAMENTOS.xlsx
+++ b/BASE_HISTORICA_AGENDAMENTOS.xlsx
@@ -415,15 +415,7 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Servico</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/BASE_HISTORICA_AGENDAMENTOS.xlsx
+++ b/BASE_HISTORICA_AGENDAMENTOS.xlsx
@@ -413,9 +413,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Horario</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Profissional</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Preco</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Servico</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>